--- a/光伏配储项目/电价数据/2026/渡美站.xlsx
+++ b/光伏配储项目/电价数据/2026/渡美站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33217</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.56496</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24735</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07321999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.05749</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17094</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25222</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24151</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27032</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.48053</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.49523</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.93432</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.17387</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.65451</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.02371</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.13754</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.92808</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.92602</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.06723</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5740299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.15042</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.60421</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.58238</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.55867</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.35973</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.57716</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.11093</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.65884</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.38728</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.67203</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44184</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.65364</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6144700000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.71509</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.5372899999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.47132</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58369</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85502</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.50498</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.33953</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.8764299999999999</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.98488</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.9643200000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.76215</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.05094</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.9749500000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.10282</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.98103</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.95948</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78408</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.80767</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.77935</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.88121</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78947</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.92906</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.77985</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.43156</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72154</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7098099999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33267</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.47044</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15152</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19392</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6741900000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6841699999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.6824</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.74115</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.68979</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.70433</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.72145</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.73658</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.48783</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.71685</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.69163</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.57211</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.48006</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.06073</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45827</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5122000000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52818</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.59346</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.63928</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5641799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.65006</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.6243200000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.56524</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70604</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6435599999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58651</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6067400000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.55777</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.47526</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.53383</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.62471</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33958</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44474</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.44553</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79112</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25399</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.16641</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.07998000000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.13625</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.21758</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.20663</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66871</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.19855</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.24296</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.25454</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.25612</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14359</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02618</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26452</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23915</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10392</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31853</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19696</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.11808</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.14616</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21954</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19773</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17989</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25263</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20642</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04937</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19414</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06057</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05877</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31653</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.18789</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7823099999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87039</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6585299999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5739500000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5756699999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.79469</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.47298</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.16632</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18462</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32468</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.6731699999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.24894</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.20925</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.22709</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.02439</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.21791</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.23895</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.23507</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.19379</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.20967</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.22522</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.22942</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.23232</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.23594</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.25046</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.18455</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21163</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.22608</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.22759</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.5460499999999999</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.02779</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.21223</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.07011000000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.09956</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.13526</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.09531000000000001</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.23884</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.20689</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.17644</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.23978</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.20164</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.23929</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.004200000000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.02605</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.01504</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20524</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.21949</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.21428</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.03355</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.25161</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.01283</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.05666</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19754</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.06545000000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.24007</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.03489</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25562</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.03206000000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.18078</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.26185</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.22924</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.24211</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.46931</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.25573</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.19735</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.23128</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.21547</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.20531</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1246</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.16104</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19268</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.15276</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18984</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.12953</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.19554</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.21366</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.24412</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.03885</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.23687</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04079</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.22584</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.16748</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.02657</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.24513</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.13455</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.01375</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.14309</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.23883</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.22808</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23239</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24582</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25694</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26152</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24802</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25596</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.23515</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2839</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30303</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.83274</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.55836</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.48587</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5602999999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.25305</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69312</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.17739</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.16803</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19621</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19807</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16028</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23846</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19511</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20078</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20787</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17373</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16489</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22321</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.24316</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.22817</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.10143</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.25683</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.25256</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.11268</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.09731000000000001</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23873</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31967</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5129199999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21195</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.2985</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5341699999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31599</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.47162</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5806399999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6685800000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6362300000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.18626</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.57655</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.48885</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6436900000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32193</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.60056</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41702</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.17674</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.11628</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.12486</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.18449</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.16717</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.12227</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.22949</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.11795</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.13492</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.12568</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.10864</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.21251</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21323</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17321</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.009779999999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25464</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00624</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17343</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.00436</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20511</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17224</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.16721</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20094</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16477</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16756</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17035</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17314</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01993</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18433</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18656</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15482</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03591</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.20663</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.23018</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.24724</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.18865</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.24307</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.27581</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.13832</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.15944</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25036</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.14205</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.15148</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24458</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.12684</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.19186</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23193</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18921</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18618</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.004070000000000001</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21752</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.03963000000000001</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01519</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.00182</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.00183</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.00236</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.00236</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.00204</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19998</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01565</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.00236</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17987</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01518</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01518</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03485</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.006480000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05547999999999999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0271</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.02273</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25268</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04223</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.15527</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25142</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26122</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.00117</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.48309</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27175</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17562</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17023</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17466</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02376</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02294</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02515</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.02265</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00556</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01136</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.02493</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8585700000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8618400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09240000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00241</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.57763</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.46386</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.64462</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.73024</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.51205</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.33293</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.62446</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6226799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.62501</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.68464</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30996</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25042</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21937</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26664</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20692</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17311</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20244</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16747</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17021</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02431</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16537</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18826</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25852</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5272100000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.52943</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29382</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.25659</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.63644</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6606300000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.5789299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.77364</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20257</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31837</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.6369400000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.68229</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.73376</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.90479</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70512</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.06209</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.58911</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.67544</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.01771</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9081699999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.62077</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.62438</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.56009</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32296</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02494</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.54675</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.56877</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.5632999999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5405399999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52712</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.6381599999999999</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.50359</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.30129</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.48014</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.68482</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.50024</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.19856</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.56504</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.57252</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.76906</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32711</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.51247</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.63679</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.22001</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.85475</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.50415</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.55027</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.55553</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.61607</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.57651</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.62009</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.5740700000000001</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.52559</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.66855</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3392</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14618</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04765</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12161</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14388</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17821</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21108</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.75842</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.30217</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.01884</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.69001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.07897</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>1.10048</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.8500800000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.89002</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5619500000000001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.91476</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.9710599999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>1.74141</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8429500000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.83399</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6418200000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.7545700000000001</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36893</v>
       </c>
     </row>
   </sheetData>
